--- a/data/nzd0056/nzd0056.xlsx
+++ b/data/nzd0056/nzd0056.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H343"/>
+  <dimension ref="A1:H344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10722,6 +10722,36 @@
       <c r="H343" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>326.91</v>
+      </c>
+      <c r="C344" t="n">
+        <v>318.82</v>
+      </c>
+      <c r="D344" t="n">
+        <v>321.25</v>
+      </c>
+      <c r="E344" t="n">
+        <v>320.05</v>
+      </c>
+      <c r="F344" t="n">
+        <v>322.3</v>
+      </c>
+      <c r="G344" t="n">
+        <v>313.88</v>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B422"/>
+  <dimension ref="A1:B423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14959,6 +14989,16 @@
       </c>
       <c r="B422" t="n">
         <v>-0.44</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -15127,28 +15167,28 @@
         <v>0.1478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0885567975730473</v>
+        <v>0.08668370865854047</v>
       </c>
       <c r="J2" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01213396493796193</v>
+        <v>0.01169331749616964</v>
       </c>
       <c r="M2" t="n">
-        <v>4.517158408995864</v>
+        <v>4.512533285776892</v>
       </c>
       <c r="N2" t="n">
-        <v>32.6530935080571</v>
+        <v>32.58624946409201</v>
       </c>
       <c r="O2" t="n">
-        <v>5.714288539097155</v>
+        <v>5.708436691782786</v>
       </c>
       <c r="P2" t="n">
-        <v>327.7275786893297</v>
+        <v>327.7482624713916</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15205,28 +15245,28 @@
         <v>0.1687</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08677652583747737</v>
+        <v>0.0833393883281303</v>
       </c>
       <c r="J3" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K3" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00758461257371601</v>
+        <v>0.007029667446337484</v>
       </c>
       <c r="M3" t="n">
-        <v>5.706574987857299</v>
+        <v>5.706694029816538</v>
       </c>
       <c r="N3" t="n">
-        <v>50.13374942649098</v>
+        <v>50.08424325733439</v>
       </c>
       <c r="O3" t="n">
-        <v>7.080519008271285</v>
+        <v>7.07702220268768</v>
       </c>
       <c r="P3" t="n">
-        <v>322.3146175737142</v>
+        <v>322.3526310603891</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15283,28 +15323,28 @@
         <v>0.1848</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1294740090411682</v>
+        <v>0.1256291188303877</v>
       </c>
       <c r="J4" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01873495037601414</v>
+        <v>0.01771908064618177</v>
       </c>
       <c r="M4" t="n">
-        <v>5.364446176293489</v>
+        <v>5.36824870642748</v>
       </c>
       <c r="N4" t="n">
-        <v>44.67499942381242</v>
+        <v>44.6657012389911</v>
       </c>
       <c r="O4" t="n">
-        <v>6.683935923077989</v>
+        <v>6.68324032479688</v>
       </c>
       <c r="P4" t="n">
-        <v>324.3023372145315</v>
+        <v>324.3448602972992</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15361,28 +15401,28 @@
         <v>0.12</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.008445370724820669</v>
+        <v>-0.0137553387623617</v>
       </c>
       <c r="J5" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K5" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L5" t="n">
-        <v>7.038803299630469e-05</v>
+        <v>0.0001870295229887686</v>
       </c>
       <c r="M5" t="n">
-        <v>5.820777896812672</v>
+        <v>5.828293774922918</v>
       </c>
       <c r="N5" t="n">
-        <v>51.55533562090994</v>
+        <v>51.63571410663805</v>
       </c>
       <c r="O5" t="n">
-        <v>7.180204427515274</v>
+        <v>7.185799475816038</v>
       </c>
       <c r="P5" t="n">
-        <v>329.2049391719729</v>
+        <v>329.2636654809116</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15439,28 +15479,28 @@
         <v>0.1227</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03308079114541877</v>
+        <v>-0.0338766604135273</v>
       </c>
       <c r="J6" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K6" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008776280413999027</v>
+        <v>0.0009259866167945496</v>
       </c>
       <c r="M6" t="n">
-        <v>6.436768729936335</v>
+        <v>6.421777089387887</v>
       </c>
       <c r="N6" t="n">
-        <v>63.39070006497318</v>
+        <v>63.21106979930067</v>
       </c>
       <c r="O6" t="n">
-        <v>7.961827683702604</v>
+        <v>7.950538962818852</v>
       </c>
       <c r="P6" t="n">
-        <v>324.5104659429771</v>
+        <v>324.5192679666773</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15517,28 +15557,28 @@
         <v>0.0252</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4036377421728674</v>
+        <v>0.4040169904285183</v>
       </c>
       <c r="J7" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K7" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05064002572988868</v>
+        <v>0.05102970490571646</v>
       </c>
       <c r="M7" t="n">
-        <v>9.460376900262123</v>
+        <v>9.434228157005299</v>
       </c>
       <c r="N7" t="n">
-        <v>155.9260229749701</v>
+        <v>155.4699453295314</v>
       </c>
       <c r="O7" t="n">
-        <v>12.48703419451433</v>
+        <v>12.4687587726097</v>
       </c>
       <c r="P7" t="n">
-        <v>302.5960859758491</v>
+        <v>302.591892567874</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -15580,7 +15620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H343"/>
+  <dimension ref="A1:H344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29973,6 +30013,48 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-35.11834015209239,173.96331710754265</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-35.11873745531504,173.96407879522056</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-35.11905630600271,173.96490865459617</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-35.119362750616006,173.9657954417573</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-35.119479050271046,173.96678999218992</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-35.11948698432844,173.96775139275022</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0056/nzd0056.xlsx
+++ b/data/nzd0056/nzd0056.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H344"/>
+  <dimension ref="A1:H346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10747,9 +10747,69 @@
         <v>322.3</v>
       </c>
       <c r="G344" t="n">
-        <v>313.88</v>
+        <v>318.52</v>
       </c>
       <c r="H344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>322.62</v>
+      </c>
+      <c r="C345" t="n">
+        <v>315.05</v>
+      </c>
+      <c r="D345" t="n">
+        <v>318.29</v>
+      </c>
+      <c r="E345" t="n">
+        <v>319.08</v>
+      </c>
+      <c r="F345" t="n">
+        <v>319.82</v>
+      </c>
+      <c r="G345" t="n">
+        <v>316.97</v>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>323.34</v>
+      </c>
+      <c r="C346" t="n">
+        <v>315.81</v>
+      </c>
+      <c r="D346" t="n">
+        <v>319.35</v>
+      </c>
+      <c r="E346" t="n">
+        <v>320.39</v>
+      </c>
+      <c r="F346" t="n">
+        <v>320.12</v>
+      </c>
+      <c r="G346" t="n">
+        <v>317.49</v>
+      </c>
+      <c r="H346" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10766,7 +10826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B423"/>
+  <dimension ref="A1:B425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14999,6 +15059,26 @@
       </c>
       <c r="B423" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -15167,28 +15247,28 @@
         <v>0.1478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08668370865854047</v>
+        <v>0.07838363218826823</v>
       </c>
       <c r="J2" t="n">
+        <v>345</v>
+      </c>
+      <c r="K2" t="n">
         <v>343</v>
       </c>
-      <c r="K2" t="n">
-        <v>341</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01169331749616964</v>
+        <v>0.00961591652803595</v>
       </c>
       <c r="M2" t="n">
-        <v>4.512533285776892</v>
+        <v>4.52404755413916</v>
       </c>
       <c r="N2" t="n">
-        <v>32.58624946409201</v>
+        <v>32.68228188490161</v>
       </c>
       <c r="O2" t="n">
-        <v>5.708436691782786</v>
+        <v>5.716841950316767</v>
       </c>
       <c r="P2" t="n">
-        <v>327.7482624713916</v>
+        <v>327.8402541080582</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15245,28 +15325,28 @@
         <v>0.1687</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0833393883281303</v>
+        <v>0.07260110726243424</v>
       </c>
       <c r="J3" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K3" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007029667446337484</v>
+        <v>0.005359476690886433</v>
       </c>
       <c r="M3" t="n">
-        <v>5.706694029816538</v>
+        <v>5.725506372073541</v>
       </c>
       <c r="N3" t="n">
-        <v>50.08424325733439</v>
+        <v>50.26883154809181</v>
       </c>
       <c r="O3" t="n">
-        <v>7.07702220268768</v>
+        <v>7.090051589945719</v>
       </c>
       <c r="P3" t="n">
-        <v>322.3526310603891</v>
+        <v>322.4718253385641</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15323,28 +15403,28 @@
         <v>0.1848</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1256291188303877</v>
+        <v>0.1152155974650418</v>
       </c>
       <c r="J4" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K4" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01771908064618177</v>
+        <v>0.01498070616461744</v>
       </c>
       <c r="M4" t="n">
-        <v>5.36824870642748</v>
+        <v>5.389354987573825</v>
       </c>
       <c r="N4" t="n">
-        <v>44.6657012389911</v>
+        <v>44.85424421277769</v>
       </c>
       <c r="O4" t="n">
-        <v>6.68324032479688</v>
+        <v>6.697331126111184</v>
       </c>
       <c r="P4" t="n">
-        <v>324.3448602972992</v>
+        <v>324.4604496397573</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15401,28 +15481,28 @@
         <v>0.12</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0137553387623617</v>
+        <v>-0.02454026356781516</v>
       </c>
       <c r="J5" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K5" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001870295229887686</v>
+        <v>0.0005968903579073315</v>
       </c>
       <c r="M5" t="n">
-        <v>5.828293774922918</v>
+        <v>5.844820828244459</v>
       </c>
       <c r="N5" t="n">
-        <v>51.63571410663805</v>
+        <v>51.81710171497684</v>
       </c>
       <c r="O5" t="n">
-        <v>7.185799475816038</v>
+        <v>7.198409665681499</v>
       </c>
       <c r="P5" t="n">
-        <v>329.2636654809116</v>
+        <v>329.3833772918268</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15479,28 +15559,28 @@
         <v>0.1227</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0338766604135273</v>
+        <v>-0.0381707350816978</v>
       </c>
       <c r="J6" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K6" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009259866167945496</v>
+        <v>0.001188558143092711</v>
       </c>
       <c r="M6" t="n">
-        <v>6.421777089387887</v>
+        <v>6.404896977581538</v>
       </c>
       <c r="N6" t="n">
-        <v>63.21106979930067</v>
+        <v>62.92057217818295</v>
       </c>
       <c r="O6" t="n">
-        <v>7.950538962818852</v>
+        <v>7.93224887268314</v>
       </c>
       <c r="P6" t="n">
-        <v>324.5192679666773</v>
+        <v>324.5669319397437</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15557,28 +15637,28 @@
         <v>0.0252</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4040169904285183</v>
+        <v>0.4113693431854634</v>
       </c>
       <c r="J7" t="n">
+        <v>345</v>
+      </c>
+      <c r="K7" t="n">
         <v>343</v>
       </c>
-      <c r="K7" t="n">
-        <v>341</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.05102970490571646</v>
+        <v>0.05337359622118365</v>
       </c>
       <c r="M7" t="n">
-        <v>9.434228157005299</v>
+        <v>9.410143407209418</v>
       </c>
       <c r="N7" t="n">
-        <v>155.4699453295314</v>
+        <v>154.7303960106244</v>
       </c>
       <c r="O7" t="n">
-        <v>12.4687587726097</v>
+        <v>12.43906732880823</v>
       </c>
       <c r="P7" t="n">
-        <v>302.591892567874</v>
+        <v>302.5104093657196</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -15620,7 +15700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H344"/>
+  <dimension ref="A1:H346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30046,10 +30126,94 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>-35.11948698432844,173.96775139275022</t>
+          <t>-35.11944534530316,173.9677464564308</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-35.11837475538569,173.96329607021775</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-35.118767864337805,173.96406030796962</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-35.11908063710068,173.96489530691065</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-35.119371174032864,173.9657925778824</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>-35.11950139947734,173.96678912069086</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-35.11945925489141,173.9677481054162</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-35.1183689478402,173.96329960095883</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-35.118761734137145,173.96406403484357</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-35.119071923937376,173.96490008682596</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-35.11935979807812,173.9657964455896</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-35.11949869594432,173.96678922611414</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-35.11945458844891,173.96774755220812</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0056/nzd0056.xlsx
+++ b/data/nzd0056/nzd0056.xlsx
@@ -10826,7 +10826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B425"/>
+  <dimension ref="A1:B426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15079,6 +15079,16 @@
       </c>
       <c r="B425" t="n">
         <v>0.64</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0056/nzd0056.xlsx
+++ b/data/nzd0056/nzd0056.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H346"/>
+  <dimension ref="A1:H347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10810,6 +10810,36 @@
         <v>317.49</v>
       </c>
       <c r="H346" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>323.69</v>
+      </c>
+      <c r="C347" t="n">
+        <v>318.48</v>
+      </c>
+      <c r="D347" t="n">
+        <v>320.07</v>
+      </c>
+      <c r="E347" t="n">
+        <v>324.92</v>
+      </c>
+      <c r="F347" t="n">
+        <v>323.58</v>
+      </c>
+      <c r="G347" t="n">
+        <v>322.94</v>
+      </c>
+      <c r="H347" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10826,7 +10856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B426"/>
+  <dimension ref="A1:B427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15089,6 +15119,16 @@
       </c>
       <c r="B426" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -15257,28 +15297,28 @@
         <v>0.1478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07838363218826823</v>
+        <v>0.07467975529873438</v>
       </c>
       <c r="J2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00961591652803595</v>
+        <v>0.008761352072552353</v>
       </c>
       <c r="M2" t="n">
-        <v>4.52404755413916</v>
+        <v>4.527535095004922</v>
       </c>
       <c r="N2" t="n">
-        <v>32.68228188490161</v>
+        <v>32.69946495032014</v>
       </c>
       <c r="O2" t="n">
-        <v>5.716841950316767</v>
+        <v>5.718344598773332</v>
       </c>
       <c r="P2" t="n">
-        <v>327.8402541080582</v>
+        <v>327.8816439955714</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15335,28 +15375,28 @@
         <v>0.1687</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07260110726243424</v>
+        <v>0.06907940150469226</v>
       </c>
       <c r="J3" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K3" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005359476690886433</v>
+        <v>0.004875530592132638</v>
       </c>
       <c r="M3" t="n">
-        <v>5.725506372073541</v>
+        <v>5.725627488652992</v>
       </c>
       <c r="N3" t="n">
-        <v>50.26883154809181</v>
+        <v>50.22425193430959</v>
       </c>
       <c r="O3" t="n">
-        <v>7.090051589945719</v>
+        <v>7.086907078148379</v>
       </c>
       <c r="P3" t="n">
-        <v>322.4718253385641</v>
+        <v>322.5112357928124</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15413,28 +15453,28 @@
         <v>0.1848</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1152155974650418</v>
+        <v>0.1107846360762997</v>
       </c>
       <c r="J4" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K4" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01498070616461744</v>
+        <v>0.01390423688834741</v>
       </c>
       <c r="M4" t="n">
-        <v>5.389354987573825</v>
+        <v>5.395560989757103</v>
       </c>
       <c r="N4" t="n">
-        <v>44.85424421277769</v>
+        <v>44.88402856903847</v>
       </c>
       <c r="O4" t="n">
-        <v>6.697331126111184</v>
+        <v>6.699554356002977</v>
       </c>
       <c r="P4" t="n">
-        <v>324.4604496397573</v>
+        <v>324.5100353272337</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15491,28 +15531,28 @@
         <v>0.12</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02454026356781516</v>
+        <v>-0.02680542779882392</v>
       </c>
       <c r="J5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005968903579073315</v>
+        <v>0.0007160264390657645</v>
       </c>
       <c r="M5" t="n">
-        <v>5.844820828244459</v>
+        <v>5.838350460219197</v>
       </c>
       <c r="N5" t="n">
-        <v>51.81710171497684</v>
+        <v>51.70900413055759</v>
       </c>
       <c r="O5" t="n">
-        <v>7.198409665681499</v>
+        <v>7.190897310527914</v>
       </c>
       <c r="P5" t="n">
-        <v>329.3833772918268</v>
+        <v>329.4087261305521</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15569,28 +15609,28 @@
         <v>0.1227</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0381707350816978</v>
+        <v>-0.0381526628500264</v>
       </c>
       <c r="J6" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K6" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001188558143092711</v>
+        <v>0.001194966083421067</v>
       </c>
       <c r="M6" t="n">
-        <v>6.404896977581538</v>
+        <v>6.386476064636538</v>
       </c>
       <c r="N6" t="n">
-        <v>62.92057217818295</v>
+        <v>62.73872346550235</v>
       </c>
       <c r="O6" t="n">
-        <v>7.93224887268314</v>
+        <v>7.920777958351209</v>
       </c>
       <c r="P6" t="n">
-        <v>324.5669319397437</v>
+        <v>324.5667296982992</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15647,28 +15687,28 @@
         <v>0.0252</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4113693431854634</v>
+        <v>0.4169928139608027</v>
       </c>
       <c r="J7" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K7" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05337359622118365</v>
+        <v>0.05500323647399552</v>
       </c>
       <c r="M7" t="n">
-        <v>9.410143407209418</v>
+        <v>9.406183762245451</v>
       </c>
       <c r="N7" t="n">
-        <v>154.7303960106244</v>
+        <v>154.5387881600321</v>
       </c>
       <c r="O7" t="n">
-        <v>12.43906732880823</v>
+        <v>12.43136308535923</v>
       </c>
       <c r="P7" t="n">
-        <v>302.5104093657196</v>
+        <v>302.4474865080057</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -15710,7 +15750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H346"/>
+  <dimension ref="A1:H347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30229,6 +30269,48 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-35.118366124727785,173.9633013172911</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-35.11874019777343,173.9640771279359</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-35.119066005562196,173.96490333356033</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-35.11932045985198,173.96580982017215</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-35.11946751519682,173.96679044199578</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-35.11940568054149,173.96774175416616</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0056/nzd0056.xlsx
+++ b/data/nzd0056/nzd0056.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H347"/>
+  <dimension ref="A1:H349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10840,6 +10840,66 @@
         <v>322.94</v>
       </c>
       <c r="H347" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>325.49</v>
+      </c>
+      <c r="C348" t="n">
+        <v>320.22</v>
+      </c>
+      <c r="D348" t="n">
+        <v>320.87</v>
+      </c>
+      <c r="E348" t="n">
+        <v>326.11</v>
+      </c>
+      <c r="F348" t="n">
+        <v>325.39</v>
+      </c>
+      <c r="G348" t="n">
+        <v>326.75</v>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>324.41</v>
+      </c>
+      <c r="C349" t="n">
+        <v>319.43</v>
+      </c>
+      <c r="D349" t="n">
+        <v>320.66</v>
+      </c>
+      <c r="E349" t="n">
+        <v>324.98</v>
+      </c>
+      <c r="F349" t="n">
+        <v>324.08</v>
+      </c>
+      <c r="G349" t="n">
+        <v>322.88</v>
+      </c>
+      <c r="H349" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10856,7 +10916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B427"/>
+  <dimension ref="A1:B430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15129,6 +15189,36 @@
       </c>
       <c r="B427" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -15297,28 +15387,28 @@
         <v>0.1478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07467975529873438</v>
+        <v>0.06891768901788657</v>
       </c>
       <c r="J2" t="n">
+        <v>348</v>
+      </c>
+      <c r="K2" t="n">
         <v>346</v>
       </c>
-      <c r="K2" t="n">
-        <v>344</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.008761352072552353</v>
+        <v>0.007532359883494544</v>
       </c>
       <c r="M2" t="n">
-        <v>4.527535095004922</v>
+        <v>4.527190065625915</v>
       </c>
       <c r="N2" t="n">
-        <v>32.69946495032014</v>
+        <v>32.64988217404746</v>
       </c>
       <c r="O2" t="n">
-        <v>5.718344598773332</v>
+        <v>5.714007540601207</v>
       </c>
       <c r="P2" t="n">
-        <v>327.8816439955714</v>
+        <v>327.9461380641315</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15375,28 +15465,28 @@
         <v>0.1687</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06907940150469226</v>
+        <v>0.06377422903039433</v>
       </c>
       <c r="J3" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K3" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004875530592132638</v>
+        <v>0.004200790701515911</v>
       </c>
       <c r="M3" t="n">
-        <v>5.725627488652992</v>
+        <v>5.717599945903914</v>
       </c>
       <c r="N3" t="n">
-        <v>50.22425193430959</v>
+        <v>50.05244059205544</v>
       </c>
       <c r="O3" t="n">
-        <v>7.086907078148379</v>
+        <v>7.07477494992282</v>
       </c>
       <c r="P3" t="n">
-        <v>322.5112357928124</v>
+        <v>322.5706980459514</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15453,28 +15543,28 @@
         <v>0.1848</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1107846360762997</v>
+        <v>0.1029369808939635</v>
       </c>
       <c r="J4" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K4" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01390423688834741</v>
+        <v>0.01210859896311522</v>
       </c>
       <c r="M4" t="n">
-        <v>5.395560989757103</v>
+        <v>5.402966861812929</v>
       </c>
       <c r="N4" t="n">
-        <v>44.88402856903847</v>
+        <v>44.8799385775699</v>
       </c>
       <c r="O4" t="n">
-        <v>6.699554356002977</v>
+        <v>6.699249105502041</v>
       </c>
       <c r="P4" t="n">
-        <v>324.5100353272337</v>
+        <v>324.597986117073</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15531,28 +15621,28 @@
         <v>0.12</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02680542779882392</v>
+        <v>-0.03048827212249709</v>
       </c>
       <c r="J5" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K5" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007160264390657645</v>
+        <v>0.0009367049707722508</v>
       </c>
       <c r="M5" t="n">
-        <v>5.838350460219197</v>
+        <v>5.821603088042065</v>
       </c>
       <c r="N5" t="n">
-        <v>51.70900413055759</v>
+        <v>51.4694934785506</v>
       </c>
       <c r="O5" t="n">
-        <v>7.190897310527914</v>
+        <v>7.174224242282269</v>
       </c>
       <c r="P5" t="n">
-        <v>329.4087261305521</v>
+        <v>329.4500099275586</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15609,28 +15699,28 @@
         <v>0.1227</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0381526628500264</v>
+        <v>-0.03676681287169681</v>
       </c>
       <c r="J6" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K6" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001194966083421067</v>
+        <v>0.00112360318978777</v>
       </c>
       <c r="M6" t="n">
-        <v>6.386476064636538</v>
+        <v>6.356648946416261</v>
       </c>
       <c r="N6" t="n">
-        <v>62.73872346550235</v>
+        <v>62.38854372909584</v>
       </c>
       <c r="O6" t="n">
-        <v>7.920777958351209</v>
+        <v>7.898641891432718</v>
       </c>
       <c r="P6" t="n">
-        <v>324.5667296982992</v>
+        <v>324.5512100979481</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15687,28 +15777,28 @@
         <v>0.0252</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4169928139608027</v>
+        <v>0.4301384977196674</v>
       </c>
       <c r="J7" t="n">
+        <v>348</v>
+      </c>
+      <c r="K7" t="n">
         <v>346</v>
       </c>
-      <c r="K7" t="n">
-        <v>344</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.05500323647399552</v>
+        <v>0.05874425088136848</v>
       </c>
       <c r="M7" t="n">
-        <v>9.406183762245451</v>
+        <v>9.406157183444172</v>
       </c>
       <c r="N7" t="n">
-        <v>154.5387881600321</v>
+        <v>154.3843837486173</v>
       </c>
       <c r="O7" t="n">
-        <v>12.43136308535923</v>
+        <v>12.42515125656896</v>
       </c>
       <c r="P7" t="n">
-        <v>302.4474865080057</v>
+        <v>302.3002143517561</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -15750,7 +15840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H347"/>
+  <dimension ref="A1:H349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30311,6 +30401,90 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-35.118351605863516,173.96331014414102</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-35.11872616283903,173.96408566050923</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-35.11905942958969,173.9649069410424</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-35.11931012596892,173.96581333358142</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-35.11945120388085,173.9667910780492</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-35.11937148987547,173.96773770086062</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-35.11836031718215,173.96330484803144</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-35.11873253502197,173.96408178652513</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-35.11906115578249,173.9649059940784</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-35.11931993881586,173.96580999731887</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-35.119463009308426,173.96679061770118</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-35.11940621897717,173.96774181799776</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0056/nzd0056.xlsx
+++ b/data/nzd0056/nzd0056.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H349"/>
+  <dimension ref="A1:H352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10900,6 +10900,96 @@
         <v>322.88</v>
       </c>
       <c r="H349" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>324.48</v>
+      </c>
+      <c r="C350" t="n">
+        <v>319.54</v>
+      </c>
+      <c r="D350" t="n">
+        <v>321.41</v>
+      </c>
+      <c r="E350" t="n">
+        <v>325.84</v>
+      </c>
+      <c r="F350" t="n">
+        <v>322.5</v>
+      </c>
+      <c r="G350" t="n">
+        <v>315.72</v>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>323.86</v>
+      </c>
+      <c r="C351" t="n">
+        <v>319.46</v>
+      </c>
+      <c r="D351" t="n">
+        <v>322.69</v>
+      </c>
+      <c r="E351" t="n">
+        <v>326.9</v>
+      </c>
+      <c r="F351" t="n">
+        <v>321.07</v>
+      </c>
+      <c r="G351" t="n">
+        <v>314.98</v>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>323.86</v>
+      </c>
+      <c r="C352" t="n">
+        <v>319.27</v>
+      </c>
+      <c r="D352" t="n">
+        <v>322.67</v>
+      </c>
+      <c r="E352" t="n">
+        <v>326.31</v>
+      </c>
+      <c r="F352" t="n">
+        <v>319.3</v>
+      </c>
+      <c r="G352" t="n">
+        <v>312.35</v>
+      </c>
+      <c r="H352" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10916,7 +11006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B430"/>
+  <dimension ref="A1:B433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15219,6 +15309,36 @@
       </c>
       <c r="B430" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -15387,28 +15507,28 @@
         <v>0.1478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06891768901788657</v>
+        <v>0.05904488049214085</v>
       </c>
       <c r="J2" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K2" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007532359883494544</v>
+        <v>0.005595981998852029</v>
       </c>
       <c r="M2" t="n">
-        <v>4.527190065625915</v>
+        <v>4.532628004606849</v>
       </c>
       <c r="N2" t="n">
-        <v>32.64988217404746</v>
+        <v>32.64392543171355</v>
       </c>
       <c r="O2" t="n">
-        <v>5.714007540601207</v>
+        <v>5.713486276496475</v>
       </c>
       <c r="P2" t="n">
-        <v>327.9461380641315</v>
+        <v>328.0571422451403</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15465,28 +15585,28 @@
         <v>0.1687</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06377422903039433</v>
+        <v>0.0553877265492163</v>
       </c>
       <c r="J3" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K3" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004200790701515911</v>
+        <v>0.003218573075610687</v>
       </c>
       <c r="M3" t="n">
-        <v>5.717599945903914</v>
+        <v>5.707555161698862</v>
       </c>
       <c r="N3" t="n">
-        <v>50.05244059205544</v>
+        <v>49.82106672169295</v>
       </c>
       <c r="O3" t="n">
-        <v>7.07477494992282</v>
+        <v>7.058403978357497</v>
       </c>
       <c r="P3" t="n">
-        <v>322.5706980459514</v>
+        <v>322.6651193334483</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15543,28 +15663,28 @@
         <v>0.1848</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1029369808939635</v>
+        <v>0.09413658558413907</v>
       </c>
       <c r="J4" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K4" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01210859896311522</v>
+        <v>0.01028529106211118</v>
       </c>
       <c r="M4" t="n">
-        <v>5.402966861812929</v>
+        <v>5.399580577819797</v>
       </c>
       <c r="N4" t="n">
-        <v>44.8799385775699</v>
+        <v>44.71566588660779</v>
       </c>
       <c r="O4" t="n">
-        <v>6.699249105502041</v>
+        <v>6.686977335583529</v>
       </c>
       <c r="P4" t="n">
-        <v>324.597986117073</v>
+        <v>324.6970618550795</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15621,28 +15741,28 @@
         <v>0.12</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03048827212249709</v>
+        <v>-0.03442704154071631</v>
       </c>
       <c r="J5" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K5" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009367049707722508</v>
+        <v>0.001215392071067245</v>
       </c>
       <c r="M5" t="n">
-        <v>5.821603088042065</v>
+        <v>5.789492212715036</v>
       </c>
       <c r="N5" t="n">
-        <v>51.4694934785506</v>
+        <v>51.07451240534247</v>
       </c>
       <c r="O5" t="n">
-        <v>7.174224242282269</v>
+        <v>7.146643436281292</v>
       </c>
       <c r="P5" t="n">
-        <v>329.4500099275586</v>
+        <v>329.4943524912514</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15699,28 +15819,28 @@
         <v>0.1227</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03676681287169681</v>
+        <v>-0.04127658872163573</v>
       </c>
       <c r="J6" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K6" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00112360318978777</v>
+        <v>0.001440632446246592</v>
       </c>
       <c r="M6" t="n">
-        <v>6.356648946416261</v>
+        <v>6.32396825701794</v>
       </c>
       <c r="N6" t="n">
-        <v>62.38854372909584</v>
+        <v>61.92666248754339</v>
       </c>
       <c r="O6" t="n">
-        <v>7.898641891432718</v>
+        <v>7.869349559369147</v>
       </c>
       <c r="P6" t="n">
-        <v>324.5512100979481</v>
+        <v>324.6019931837146</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15777,28 +15897,28 @@
         <v>0.0252</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4301384977196674</v>
+        <v>0.4310383560943838</v>
       </c>
       <c r="J7" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K7" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05874425088136848</v>
+        <v>0.06000732229553751</v>
       </c>
       <c r="M7" t="n">
-        <v>9.406157183444172</v>
+        <v>9.337516391347418</v>
       </c>
       <c r="N7" t="n">
-        <v>154.3843837486173</v>
+        <v>153.0776242891769</v>
       </c>
       <c r="O7" t="n">
-        <v>12.42515125656896</v>
+        <v>12.37245425488318</v>
       </c>
       <c r="P7" t="n">
-        <v>302.3002143517561</v>
+        <v>302.2900925861939</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -15840,7 +15960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H349"/>
+  <dimension ref="A1:H352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30485,6 +30605,132 @@
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-35.11835975255966,173.96330519129785</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-35.118731647756,173.9640823259407</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-35.11905499080819,173.9649093760925</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-35.119312470631485,173.9658125364214</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-35.11947724791571,173.96679006247209</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-35.119470472301245,173.96774943524358</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-35.11836475350175,173.96330215093818</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-35.11873229304035,173.96408193363848</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-35.119044469251826,173.964915148062</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-35.119303265659944,173.96581566601228</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-35.119490134756425,173.96678955995455</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-35.11947711300783,173.9677502225016</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-35.11836475350175,173.96330215093818</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-35.11873382559065,173.9640810019207</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-35.11904463365115,173.96491505787498</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-35.11930838918185,173.96581392407026</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-35.11950608560123,173.96678893795715</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-35.119500714437955,173.9677530204602</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0056/nzd0056.xlsx
+++ b/data/nzd0056/nzd0056.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H352"/>
+  <dimension ref="A1:H355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10990,6 +10990,96 @@
         <v>312.35</v>
       </c>
       <c r="H352" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>322.11</v>
+      </c>
+      <c r="C353" t="n">
+        <v>317.33</v>
+      </c>
+      <c r="D353" t="n">
+        <v>321.17</v>
+      </c>
+      <c r="E353" t="n">
+        <v>324.41</v>
+      </c>
+      <c r="F353" t="n">
+        <v>316</v>
+      </c>
+      <c r="G353" t="n">
+        <v>312.35</v>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>322.17</v>
+      </c>
+      <c r="C354" t="n">
+        <v>316.94</v>
+      </c>
+      <c r="D354" t="n">
+        <v>321.96</v>
+      </c>
+      <c r="E354" t="n">
+        <v>322.85</v>
+      </c>
+      <c r="F354" t="n">
+        <v>314.28</v>
+      </c>
+      <c r="G354" t="n">
+        <v>308.25</v>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>322.17</v>
+      </c>
+      <c r="C355" t="n">
+        <v>317.11</v>
+      </c>
+      <c r="D355" t="n">
+        <v>322.33</v>
+      </c>
+      <c r="E355" t="n">
+        <v>323.74</v>
+      </c>
+      <c r="F355" t="n">
+        <v>313.59</v>
+      </c>
+      <c r="G355" t="n">
+        <v>306.73</v>
+      </c>
+      <c r="H355" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11006,7 +11096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B433"/>
+  <dimension ref="A1:B436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15339,6 +15429,36 @@
       </c>
       <c r="B433" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>
@@ -15507,28 +15627,28 @@
         <v>0.1478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05904488049214085</v>
+        <v>0.04637330517872019</v>
       </c>
       <c r="J2" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K2" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005595981998852029</v>
+        <v>0.003472657371326848</v>
       </c>
       <c r="M2" t="n">
-        <v>4.532628004606849</v>
+        <v>4.552167655146129</v>
       </c>
       <c r="N2" t="n">
-        <v>32.64392543171355</v>
+        <v>32.83149108440918</v>
       </c>
       <c r="O2" t="n">
-        <v>5.713486276496475</v>
+        <v>5.729877056657427</v>
       </c>
       <c r="P2" t="n">
-        <v>328.0571422451403</v>
+        <v>328.2000491832674</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15585,28 +15705,28 @@
         <v>0.1687</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0553877265492163</v>
+        <v>0.04349472161540729</v>
       </c>
       <c r="J3" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K3" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003218573075610687</v>
+        <v>0.002007142720677368</v>
       </c>
       <c r="M3" t="n">
-        <v>5.707555161698862</v>
+        <v>5.71529027086441</v>
       </c>
       <c r="N3" t="n">
-        <v>49.82106672169295</v>
+        <v>49.80649798256276</v>
       </c>
       <c r="O3" t="n">
-        <v>7.058403978357497</v>
+        <v>7.057371889206546</v>
       </c>
       <c r="P3" t="n">
-        <v>322.6651193334483</v>
+        <v>322.7994277741296</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15663,28 +15783,28 @@
         <v>0.1848</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09413658558413907</v>
+        <v>0.08498642058261867</v>
       </c>
       <c r="J4" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01028529106211118</v>
+        <v>0.008505767891706872</v>
       </c>
       <c r="M4" t="n">
-        <v>5.399580577819797</v>
+        <v>5.397935079388657</v>
       </c>
       <c r="N4" t="n">
-        <v>44.71566588660779</v>
+        <v>44.57993781094305</v>
       </c>
       <c r="O4" t="n">
-        <v>6.686977335583529</v>
+        <v>6.676820935965188</v>
       </c>
       <c r="P4" t="n">
-        <v>324.6970618550795</v>
+        <v>324.8003874760822</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15741,28 +15861,28 @@
         <v>0.12</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03442704154071631</v>
+        <v>-0.04272289880167958</v>
       </c>
       <c r="J5" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K5" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001215392071067245</v>
+        <v>0.001897257126962981</v>
       </c>
       <c r="M5" t="n">
-        <v>5.789492212715036</v>
+        <v>5.777013231571013</v>
       </c>
       <c r="N5" t="n">
-        <v>51.07451240534247</v>
+        <v>50.84335471438526</v>
       </c>
       <c r="O5" t="n">
-        <v>7.146643436281292</v>
+        <v>7.13045263040049</v>
       </c>
       <c r="P5" t="n">
-        <v>329.4943524912514</v>
+        <v>329.5880411088458</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15819,28 +15939,28 @@
         <v>0.1227</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04127658872163573</v>
+        <v>-0.05629220144537682</v>
       </c>
       <c r="J6" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K6" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001440632446246592</v>
+        <v>0.002696357097029867</v>
       </c>
       <c r="M6" t="n">
-        <v>6.32396825701794</v>
+        <v>6.343914652087456</v>
       </c>
       <c r="N6" t="n">
-        <v>61.92666248754339</v>
+        <v>62.05977269688636</v>
       </c>
       <c r="O6" t="n">
-        <v>7.869349559369147</v>
+        <v>7.877802529696106</v>
       </c>
       <c r="P6" t="n">
-        <v>324.6019931837146</v>
+        <v>324.7715778559795</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15897,28 +16017,28 @@
         <v>0.0252</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4310383560943838</v>
+        <v>0.4229674881853617</v>
       </c>
       <c r="J7" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K7" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06000732229553751</v>
+        <v>0.05882317105478996</v>
       </c>
       <c r="M7" t="n">
-        <v>9.337516391347418</v>
+        <v>9.304178050968467</v>
       </c>
       <c r="N7" t="n">
-        <v>153.0776242891769</v>
+        <v>152.0096849256552</v>
       </c>
       <c r="O7" t="n">
-        <v>12.37245425488318</v>
+        <v>12.3292207752824</v>
       </c>
       <c r="P7" t="n">
-        <v>302.2900925861939</v>
+        <v>302.3812651819555</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -15960,7 +16080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H352"/>
+  <dimension ref="A1:H355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30731,6 +30851,132 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-35.11837886906367,173.96329356927586</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-35.118749473735505,173.96407148858984</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-35.119056963599974,173.96490829384803</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-35.11932488865899,173.9658083144251</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-35.11953582446428,173.96678777830053</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-35.119500714437955,173.9677530204602</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-35.118378385101565,173.96329386350436</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-35.11875261949649,173.9640695761157</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-35.11905046982697,173.96491185623583</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-35.11933843559789,173.9658037086095</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-35.11955132472013,173.9667871738732</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-35.119537507541544,173.9677573823004</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-35.118378385101565,173.96329386350436</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-35.11875124826734,173.9640704097583</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-35.11904742843958,173.96491352469573</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-35.11933070689558,173.9658063362865</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-35.119557542845996,173.9667869313994</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-35.11955114791154,173.96775899937396</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
